--- a/res/CheatSheets.xlsx
+++ b/res/CheatSheets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dvdbrdhrst/GitHub/QC-MXP/res/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF306F7A-6081-A240-92C3-9CEFBC36EADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD4D968-77D3-E949-995D-B6CDDC65CDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="760" windowWidth="27700" windowHeight="16940" activeTab="2" xr2:uid="{D81271CA-93EF-834F-B9E5-659B6E5E8FF3}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{D81271CA-93EF-834F-B9E5-659B6E5E8FF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Prefilter" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="85">
   <si>
     <t>Action</t>
   </si>
@@ -145,16 +145,10 @@
     <t>↓ Complete</t>
   </si>
   <si>
-    <t>% missing QC calculated per batch and peak kept if every batch has &lt;= specified % missing QCs</t>
-  </si>
-  <si>
     <t>% missing QC calculated per batch and peak kept if any batch has &lt;= specified % missing QCs</t>
   </si>
   <si>
     <t xml:space="preserve">% missing QC calculated across all batches </t>
-  </si>
-  <si>
-    <t>"Mean","Linear","Spline","Sample"</t>
   </si>
   <si>
     <t>"QC","Reference","Sample"</t>
@@ -261,9 +255,6 @@
     <t>QC' = both the intra- and inter-batch based on the QC samples; 'Reference' = intra-batch correction based on the QCs but the inter-batch correction uses the samples labelled as 'Reference'. 'Sample' = both the intra-batch &amp; inter-batch correction uses the samples labelled as 'Sample'.                                                                 N.B. The 'Sample' option is not recommended and is primarily included to illustrate how poor this approach is to between-batch correction (or as a last resort for data with no QCs).</t>
   </si>
   <si>
-    <t>Three correction modes. "Spline" is the default QCRSC algorithm that requires optimisation of the smoothing parameter. "Linear" is a simple Robust (bisquare) linear regression based on the QC values &amp; requires no smoothing optimisation. "Mean" equalises the QC mean across batches &amp; ignores within batch systematic change. "Sample" ignores the QCs and corrects using linear regression based on the samples labelled 'Sample'.                      N.B. If the number of QC samples in a batch is 5 or less then the Spline Algorithm switches to a linear correction (N&lt;=5 is too few for effectively fitting a non-linear curve with cross-validation).  N.B. The 'Sample' option is not recommended and is primarily included to illustrate how poor this approach is to within-batch correction (or as a last resort for data with no QCs).</t>
-  </si>
-  <si>
     <t>% missing per feature &lt;=</t>
   </si>
   <si>
@@ -301,6 +292,27 @@
   </si>
   <si>
     <t>Leave on 'Complete' unless performing large scale studies over many batches. For QC filtering: 'Median' / 'Min' / 'Max' referes to filtering on the median/max/min batch QC statistics. Alternatively choose a specific (representative) batch to filter on. 'Complete' calulates the stats across all batches. For Reference filtering only the 'Complete' option is available.</t>
+  </si>
+  <si>
+    <t>↓ N Batch</t>
+  </si>
+  <si>
+    <t>% missing QC calculated per batch and peak kept if every batch have &lt;= specified % missing QCs</t>
+  </si>
+  <si>
+    <t>% missing QC calculated per batch and peak kept if N batches have &lt;= specified % missing QCs</t>
+  </si>
+  <si>
+    <t>"Sample","Mean","Linear","Spline","Spline-C2", "Spline-C4","Spline-C6"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batch Select Tab: </t>
+  </si>
+  <si>
+    <t>Select batches to explore: set the tickbox for the batches you want to include in the visualisations and cleaning and then  press "Send" for the selection to be processed.</t>
+  </si>
+  <si>
+    <t>Three fundemental correction modes. "Spline" is the default QCRSC algorithm that requires optimisation of the smoothing parameter ("Spline-C2","-C4" &amp; "-C6" constrains the spline model to limit  degree of non-linearity - this is useful if your batches do not start and end with QC sample which forces the algorithm to extrapolate). "Linear" is a simple Robust (bisquare) linear regression based on the QC values &amp; requires no smoothing optimisation. "Mean" equalises the QC mean across batches &amp; ignores within batch systematic change. "Sample" ignores the QCs and corrects using linear regression based on the samples labelled 'Sample'.                                                                                                                N.B. If the number of QC samples in a batch is 5 or less then the Spline Algorithm switches to a linear correction (N&lt;=5 is too few for effectively fitting a non-linear curve with cross-validation).                N.B. The 'Sample' option is not recommended and is primarily included to illustrate how poor this approach is to within-batch correction (or as a last resort for data with no QCs).</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EE47B5D-1EEA-F146-A9A9-111FDB4E8BA0}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1046,50 +1058,58 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B8" s="21" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1109,7 +1129,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B1" s="28" t="s">
         <v>10</v>
@@ -1120,18 +1140,18 @@
     </row>
     <row r="2" spans="1:3" ht="40" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="40" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>6</v>
@@ -1142,7 +1162,7 @@
     </row>
     <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>3</v>
@@ -1153,7 +1173,7 @@
     </row>
     <row r="5" spans="1:3" ht="40" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>4</v>
@@ -1164,40 +1184,40 @@
     </row>
     <row r="6" spans="1:3" ht="40" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="340" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="260" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>59</v>
-      </c>
       <c r="B7" s="12" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="160" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="40" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>7</v>
@@ -1208,7 +1228,7 @@
     </row>
     <row r="10" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>5</v>
@@ -1219,7 +1239,7 @@
     </row>
     <row r="11" spans="1:3" ht="141" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B11" s="36" t="s">
         <v>8</v>
@@ -1236,7 +1256,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C14340D4-650A-D548-A81E-733CEBC5D446}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.140625" style="1" customWidth="1"/>
@@ -1251,157 +1271,165 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="40" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="80" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="47" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="23"/>
+    </row>
+    <row r="8" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="37" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="6"/>
+    </row>
+    <row r="12" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="80" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="47" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="23"/>
-    </row>
-    <row r="7" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="37" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="6"/>
-    </row>
-    <row r="11" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="40" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="22" t="s">
+    </row>
+    <row r="13" spans="1:2" ht="40" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="23"/>
-    </row>
-    <row r="14" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>70</v>
-      </c>
+      <c r="B14" s="23"/>
     </row>
     <row r="15" spans="1:2" ht="20" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+      <c r="A16" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B16" s="23" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
+    <row r="17" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B17" s="23" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+    <row r="18" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A18" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="23" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="33" t="s">
+      <c r="B18" s="23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="6"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="38" t="s">
-        <v>77</v>
-      </c>
+      <c r="B19" s="6"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="38"/>
-    </row>
-    <row r="21" spans="1:2" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="34" t="s">
+      <c r="B21" s="38"/>
+    </row>
+    <row r="22" spans="1:2" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="39"/>
+      <c r="B22" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B20:B22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
